--- a/optimized_benchmark_results/shaker_benchmark.xlsx
+++ b/optimized_benchmark_results/shaker_benchmark.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\afons\OneDrive - Universidade de Lisboa\Controlo de Plataforma Sismica\minimesa_data\optimized_benchmark_results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDC98FF1-B27A-4EC0-995C-946D7D5EF541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F619F89-21D4-4477-96DA-D1A215BD67D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28740" yWindow="-60" windowWidth="28920" windowHeight="16320" xr2:uid="{40A5E321-79F6-4163-A8DE-342D0D4D7873}"/>
   </bookViews>
   <sheets>
-    <sheet name="Folha1" sheetId="1" r:id="rId1"/>
+    <sheet name="comJiji" sheetId="3" r:id="rId1"/>
+    <sheet name="Folha1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="23">
   <si>
     <t>N</t>
   </si>
@@ -102,6 +103,9 @@
   </si>
   <si>
     <t>mediana MSE Disp</t>
+  </si>
+  <si>
+    <t>Jiji</t>
   </si>
 </sst>
 </file>
@@ -179,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -218,6 +222,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -332,7 +338,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Folha1!$G$7</c:f>
+              <c:f>comJiji!$G$7</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -370,13 +376,13 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Folha1!$D$8:$F$35</c15:sqref>
+                    <c15:sqref>comJiji!$D$8:$F$39</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Folha1!$D$8:$F$8,Folha1!$D$10:$F$10,Folha1!$D$12:$F$12,Folha1!$D$14:$F$14,Folha1!$D$16:$F$16,Folha1!$D$18:$F$18,Folha1!$D$20:$F$20,Folha1!$D$22:$F$22,Folha1!$D$24:$F$24,Folha1!$D$26:$F$26,Folha1!$D$28:$F$28,Folha1!$D$30:$F$30,Folha1!$D$32:$F$32,Folha1!$D$34:$F$34)</c:f>
+              <c:f>(comJiji!$D$8:$F$8,comJiji!$D$10:$F$10,comJiji!$D$12:$F$12,comJiji!$D$14:$F$14,comJiji!$D$16:$F$16,comJiji!$D$18:$F$18,comJiji!$D$20:$F$20,comJiji!$D$22:$F$22,comJiji!$D$24:$F$24,comJiji!$D$26:$F$26,comJiji!$D$28:$F$28,comJiji!$D$30:$F$30,comJiji!$D$32:$F$32,comJiji!$D$34:$F$34,comJiji!$D$36:$F$36,comJiji!$D$38:$F$38)</c:f>
               <c:multiLvlStrCache>
-                <c:ptCount val="14"/>
+                <c:ptCount val="16"/>
                 <c:lvl>
                   <c:pt idx="0">
                     <c:v>acc</c:v>
@@ -418,6 +424,12 @@
                     <c:v>acc</c:v>
                   </c:pt>
                   <c:pt idx="13">
+                    <c:v>acc</c:v>
+                  </c:pt>
+                  <c:pt idx="14">
+                    <c:v>acc</c:v>
+                  </c:pt>
+                  <c:pt idx="15">
                     <c:v>acc</c:v>
                   </c:pt>
                 </c:lvl>
@@ -444,10 +456,10 @@
                     <c:v>N</c:v>
                   </c:pt>
                   <c:pt idx="7">
+                    <c:v>P</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
                     <c:v>N</c:v>
-                  </c:pt>
-                  <c:pt idx="8">
-                    <c:v>P</c:v>
                   </c:pt>
                   <c:pt idx="9">
                     <c:v>N</c:v>
@@ -462,6 +474,12 @@
                     <c:v>P</c:v>
                   </c:pt>
                   <c:pt idx="13">
+                    <c:v>N</c:v>
+                  </c:pt>
+                  <c:pt idx="14">
+                    <c:v>P</c:v>
+                  </c:pt>
+                  <c:pt idx="15">
                     <c:v>N</c:v>
                   </c:pt>
                 </c:lvl>
@@ -473,21 +491,24 @@
                     <c:v>Erzikan</c:v>
                   </c:pt>
                   <c:pt idx="4">
+                    <c:v>Jiji</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
                     <c:v>Kobe</c:v>
                   </c:pt>
-                  <c:pt idx="6">
+                  <c:pt idx="8">
                     <c:v>L'Aquila</c:v>
                   </c:pt>
-                  <c:pt idx="7">
+                  <c:pt idx="9">
                     <c:v>Newhall</c:v>
                   </c:pt>
-                  <c:pt idx="9">
+                  <c:pt idx="11">
                     <c:v>Rinaldi</c:v>
                   </c:pt>
-                  <c:pt idx="11">
+                  <c:pt idx="13">
                     <c:v>Sylmar</c:v>
                   </c:pt>
-                  <c:pt idx="13">
+                  <c:pt idx="15">
                     <c:v>Tolmezzo</c:v>
                   </c:pt>
                 </c:lvl>
@@ -499,14 +520,14 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Folha1!$G$8:$G$35</c15:sqref>
+                    <c15:sqref>comJiji!$G$8:$G$39</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Folha1!$G$8,Folha1!$G$10,Folha1!$G$12,Folha1!$G$14,Folha1!$G$16,Folha1!$G$18,Folha1!$G$20,Folha1!$G$22,Folha1!$G$24,Folha1!$G$26,Folha1!$G$28,Folha1!$G$30,Folha1!$G$32,Folha1!$G$34)</c:f>
+              <c:f>(comJiji!$G$8,comJiji!$G$10,comJiji!$G$12,comJiji!$G$14,comJiji!$G$16,comJiji!$G$18,comJiji!$G$20,comJiji!$G$22,comJiji!$G$24,comJiji!$G$26,comJiji!$G$28,comJiji!$G$30,comJiji!$G$32,comJiji!$G$34,comJiji!$G$36,comJiji!$G$38)</c:f>
               <c:numCache>
                 <c:formatCode>0.00E+00</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>5.6199999999999997E-5</c:v>
                 </c:pt>
@@ -520,33 +541,39 @@
                   <c:v>4.1099999999999996E-6</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>4.28E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>3.1000000000000001E-5</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
                   <c:v>2.09E-5</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="8">
                   <c:v>1.98E-5</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="9">
                   <c:v>1.34E-5</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="10">
                   <c:v>6.7499999999999997E-6</c:v>
                 </c:pt>
-                <c:pt idx="9">
-                  <c:v>1.2999999999999999E-5</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1.9300000000000002E-5</c:v>
-                </c:pt>
                 <c:pt idx="11">
+                  <c:v>1.8E-5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>5.8900000000000002E-5</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>1.8600000000000001E-5</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="14">
                   <c:v>4.9799999999999998E-6</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="15">
                   <c:v>3.0400000000000002E-4</c:v>
                 </c:pt>
               </c:numCache>
@@ -555,7 +582,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-DA05-4E58-AC06-AF98CDCBEC7D}"/>
+              <c16:uniqueId val="{00000000-65FD-4B9D-97FA-E6B30D32ED66}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -564,7 +591,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Folha1!$H$7</c:f>
+              <c:f>comJiji!$H$7</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -602,13 +629,13 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Folha1!$D$8:$F$35</c15:sqref>
+                    <c15:sqref>comJiji!$D$8:$F$39</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Folha1!$D$8:$F$8,Folha1!$D$10:$F$10,Folha1!$D$12:$F$12,Folha1!$D$14:$F$14,Folha1!$D$16:$F$16,Folha1!$D$18:$F$18,Folha1!$D$20:$F$20,Folha1!$D$22:$F$22,Folha1!$D$24:$F$24,Folha1!$D$26:$F$26,Folha1!$D$28:$F$28,Folha1!$D$30:$F$30,Folha1!$D$32:$F$32,Folha1!$D$34:$F$34)</c:f>
+              <c:f>(comJiji!$D$8:$F$8,comJiji!$D$10:$F$10,comJiji!$D$12:$F$12,comJiji!$D$14:$F$14,comJiji!$D$16:$F$16,comJiji!$D$18:$F$18,comJiji!$D$20:$F$20,comJiji!$D$22:$F$22,comJiji!$D$24:$F$24,comJiji!$D$26:$F$26,comJiji!$D$28:$F$28,comJiji!$D$30:$F$30,comJiji!$D$32:$F$32,comJiji!$D$34:$F$34,comJiji!$D$36:$F$36,comJiji!$D$38:$F$38)</c:f>
               <c:multiLvlStrCache>
-                <c:ptCount val="14"/>
+                <c:ptCount val="16"/>
                 <c:lvl>
                   <c:pt idx="0">
                     <c:v>acc</c:v>
@@ -650,6 +677,12 @@
                     <c:v>acc</c:v>
                   </c:pt>
                   <c:pt idx="13">
+                    <c:v>acc</c:v>
+                  </c:pt>
+                  <c:pt idx="14">
+                    <c:v>acc</c:v>
+                  </c:pt>
+                  <c:pt idx="15">
                     <c:v>acc</c:v>
                   </c:pt>
                 </c:lvl>
@@ -676,10 +709,10 @@
                     <c:v>N</c:v>
                   </c:pt>
                   <c:pt idx="7">
+                    <c:v>P</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
                     <c:v>N</c:v>
-                  </c:pt>
-                  <c:pt idx="8">
-                    <c:v>P</c:v>
                   </c:pt>
                   <c:pt idx="9">
                     <c:v>N</c:v>
@@ -694,6 +727,12 @@
                     <c:v>P</c:v>
                   </c:pt>
                   <c:pt idx="13">
+                    <c:v>N</c:v>
+                  </c:pt>
+                  <c:pt idx="14">
+                    <c:v>P</c:v>
+                  </c:pt>
+                  <c:pt idx="15">
                     <c:v>N</c:v>
                   </c:pt>
                 </c:lvl>
@@ -705,21 +744,24 @@
                     <c:v>Erzikan</c:v>
                   </c:pt>
                   <c:pt idx="4">
+                    <c:v>Jiji</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
                     <c:v>Kobe</c:v>
                   </c:pt>
-                  <c:pt idx="6">
+                  <c:pt idx="8">
                     <c:v>L'Aquila</c:v>
                   </c:pt>
-                  <c:pt idx="7">
+                  <c:pt idx="9">
                     <c:v>Newhall</c:v>
                   </c:pt>
-                  <c:pt idx="9">
+                  <c:pt idx="11">
                     <c:v>Rinaldi</c:v>
                   </c:pt>
-                  <c:pt idx="11">
+                  <c:pt idx="13">
                     <c:v>Sylmar</c:v>
                   </c:pt>
-                  <c:pt idx="13">
+                  <c:pt idx="15">
                     <c:v>Tolmezzo</c:v>
                   </c:pt>
                 </c:lvl>
@@ -731,14 +773,14 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Folha1!$H$8:$H$35</c15:sqref>
+                    <c15:sqref>comJiji!$H$8:$H$39</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Folha1!$H$8,Folha1!$H$10,Folha1!$H$12,Folha1!$H$14,Folha1!$H$16,Folha1!$H$18,Folha1!$H$20,Folha1!$H$22,Folha1!$H$24,Folha1!$H$26,Folha1!$H$28,Folha1!$H$30,Folha1!$H$32,Folha1!$H$34)</c:f>
+              <c:f>(comJiji!$H$8,comJiji!$H$10,comJiji!$H$12,comJiji!$H$14,comJiji!$H$16,comJiji!$H$18,comJiji!$H$20,comJiji!$H$22,comJiji!$H$24,comJiji!$H$26,comJiji!$H$28,comJiji!$H$30,comJiji!$H$32,comJiji!$H$34,comJiji!$H$36,comJiji!$H$38)</c:f>
               <c:numCache>
                 <c:formatCode>0.00E+00</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>1.11E-5</c:v>
                 </c:pt>
@@ -752,33 +794,39 @@
                   <c:v>7.0300000000000001E-8</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>2.2100000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.5100000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>3.0800000000000001E-7</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
                   <c:v>1.19E-6</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="8">
                   <c:v>4.1199999999999998E-7</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="9">
                   <c:v>8.8800000000000001E-7</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="10">
                   <c:v>1.61E-6</c:v>
                 </c:pt>
-                <c:pt idx="9">
-                  <c:v>1.28E-6</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>2.1000000000000001E-4</c:v>
-                </c:pt>
                 <c:pt idx="11">
+                  <c:v>1.91E-5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4.32E-5</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>3.0900000000000001E-6</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="14">
                   <c:v>4.3000000000000001E-7</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="15">
                   <c:v>8.7399999999999997E-5</c:v>
                 </c:pt>
               </c:numCache>
@@ -787,7 +835,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-DA05-4E58-AC06-AF98CDCBEC7D}"/>
+              <c16:uniqueId val="{00000001-65FD-4B9D-97FA-E6B30D32ED66}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -796,7 +844,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Folha1!$I$7</c:f>
+              <c:f>comJiji!$I$7</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -834,13 +882,13 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Folha1!$D$8:$F$35</c15:sqref>
+                    <c15:sqref>comJiji!$D$8:$F$39</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Folha1!$D$8:$F$8,Folha1!$D$10:$F$10,Folha1!$D$12:$F$12,Folha1!$D$14:$F$14,Folha1!$D$16:$F$16,Folha1!$D$18:$F$18,Folha1!$D$20:$F$20,Folha1!$D$22:$F$22,Folha1!$D$24:$F$24,Folha1!$D$26:$F$26,Folha1!$D$28:$F$28,Folha1!$D$30:$F$30,Folha1!$D$32:$F$32,Folha1!$D$34:$F$34)</c:f>
+              <c:f>(comJiji!$D$8:$F$8,comJiji!$D$10:$F$10,comJiji!$D$12:$F$12,comJiji!$D$14:$F$14,comJiji!$D$16:$F$16,comJiji!$D$18:$F$18,comJiji!$D$20:$F$20,comJiji!$D$22:$F$22,comJiji!$D$24:$F$24,comJiji!$D$26:$F$26,comJiji!$D$28:$F$28,comJiji!$D$30:$F$30,comJiji!$D$32:$F$32,comJiji!$D$34:$F$34,comJiji!$D$36:$F$36,comJiji!$D$38:$F$38)</c:f>
               <c:multiLvlStrCache>
-                <c:ptCount val="14"/>
+                <c:ptCount val="16"/>
                 <c:lvl>
                   <c:pt idx="0">
                     <c:v>acc</c:v>
@@ -882,6 +930,12 @@
                     <c:v>acc</c:v>
                   </c:pt>
                   <c:pt idx="13">
+                    <c:v>acc</c:v>
+                  </c:pt>
+                  <c:pt idx="14">
+                    <c:v>acc</c:v>
+                  </c:pt>
+                  <c:pt idx="15">
                     <c:v>acc</c:v>
                   </c:pt>
                 </c:lvl>
@@ -908,10 +962,10 @@
                     <c:v>N</c:v>
                   </c:pt>
                   <c:pt idx="7">
+                    <c:v>P</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
                     <c:v>N</c:v>
-                  </c:pt>
-                  <c:pt idx="8">
-                    <c:v>P</c:v>
                   </c:pt>
                   <c:pt idx="9">
                     <c:v>N</c:v>
@@ -926,6 +980,12 @@
                     <c:v>P</c:v>
                   </c:pt>
                   <c:pt idx="13">
+                    <c:v>N</c:v>
+                  </c:pt>
+                  <c:pt idx="14">
+                    <c:v>P</c:v>
+                  </c:pt>
+                  <c:pt idx="15">
                     <c:v>N</c:v>
                   </c:pt>
                 </c:lvl>
@@ -937,21 +997,24 @@
                     <c:v>Erzikan</c:v>
                   </c:pt>
                   <c:pt idx="4">
+                    <c:v>Jiji</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
                     <c:v>Kobe</c:v>
                   </c:pt>
-                  <c:pt idx="6">
+                  <c:pt idx="8">
                     <c:v>L'Aquila</c:v>
                   </c:pt>
-                  <c:pt idx="7">
+                  <c:pt idx="9">
                     <c:v>Newhall</c:v>
                   </c:pt>
-                  <c:pt idx="9">
+                  <c:pt idx="11">
                     <c:v>Rinaldi</c:v>
                   </c:pt>
-                  <c:pt idx="11">
+                  <c:pt idx="13">
                     <c:v>Sylmar</c:v>
                   </c:pt>
-                  <c:pt idx="13">
+                  <c:pt idx="15">
                     <c:v>Tolmezzo</c:v>
                   </c:pt>
                 </c:lvl>
@@ -963,14 +1026,14 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Folha1!$I$8:$I$35</c15:sqref>
+                    <c15:sqref>comJiji!$I$8:$I$39</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Folha1!$I$8,Folha1!$I$10,Folha1!$I$12,Folha1!$I$14,Folha1!$I$16,Folha1!$I$18,Folha1!$I$20,Folha1!$I$22,Folha1!$I$24,Folha1!$I$26,Folha1!$I$28,Folha1!$I$30,Folha1!$I$32,Folha1!$I$34)</c:f>
+              <c:f>(comJiji!$I$8,comJiji!$I$10,comJiji!$I$12,comJiji!$I$14,comJiji!$I$16,comJiji!$I$18,comJiji!$I$20,comJiji!$I$22,comJiji!$I$24,comJiji!$I$26,comJiji!$I$28,comJiji!$I$30,comJiji!$I$32,comJiji!$I$34,comJiji!$I$36,comJiji!$I$38)</c:f>
               <c:numCache>
                 <c:formatCode>0.00E+00</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>4.9100000000000001E-5</c:v>
                 </c:pt>
@@ -984,33 +1047,39 @@
                   <c:v>7.0999999999999998E-6</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>0.17499999999999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.189</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>1.9000000000000001E-5</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
                   <c:v>1.7099999999999999E-5</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="8">
                   <c:v>4.0200000000000001E-5</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="9">
                   <c:v>1.4399999999999999E-5</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="10">
                   <c:v>2.51E-5</c:v>
                 </c:pt>
-                <c:pt idx="9">
-                  <c:v>3.1300000000000002E-5</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>2.7999999999999998E-4</c:v>
-                </c:pt>
                 <c:pt idx="11">
+                  <c:v>3.8999999999999999E-5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>6.4999999999999994E-5</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>5.0099999999999998E-5</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="14">
                   <c:v>9.8099999999999992E-6</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="15">
                   <c:v>1.67E-3</c:v>
                 </c:pt>
               </c:numCache>
@@ -1019,7 +1088,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-DA05-4E58-AC06-AF98CDCBEC7D}"/>
+              <c16:uniqueId val="{00000002-65FD-4B9D-97FA-E6B30D32ED66}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1089,8 +1158,7 @@
         <c:scaling>
           <c:logBase val="10"/>
           <c:orientation val="minMax"/>
-          <c:max val="2.0000000000000005E-3"/>
-          <c:min val="7.0000000000000031E-8"/>
+          <c:max val="5"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -1367,7 +1435,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Folha1!$G$7</c:f>
+              <c:f>comJiji!$G$7</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1405,13 +1473,13 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Folha1!$D$8:$F$35</c15:sqref>
+                    <c15:sqref>comJiji!$D$8:$F$39</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Folha1!$D$9:$F$9,Folha1!$D$11:$F$11,Folha1!$D$13:$F$13,Folha1!$D$15:$F$15,Folha1!$D$17:$F$17,Folha1!$D$19:$F$19,Folha1!$D$21:$F$21,Folha1!$D$23:$F$23,Folha1!$D$25:$F$25,Folha1!$D$27:$F$27,Folha1!$D$29:$F$29,Folha1!$D$31:$F$31,Folha1!$D$33:$F$33,Folha1!$D$35:$F$35)</c:f>
+              <c:f>(comJiji!$D$9:$F$9,comJiji!$D$11:$F$11,comJiji!$D$13:$F$13,comJiji!$D$15:$F$15,comJiji!$D$17:$F$17,comJiji!$D$19:$F$19,comJiji!$D$21:$F$21,comJiji!$D$23:$F$23,comJiji!$D$25:$F$25,comJiji!$D$27:$F$27,comJiji!$D$29:$F$29,comJiji!$D$31:$F$31,comJiji!$D$33:$F$33,comJiji!$D$35:$F$35,comJiji!$D$37:$F$37,comJiji!$D$39:$F$39)</c:f>
               <c:multiLvlStrCache>
-                <c:ptCount val="14"/>
+                <c:ptCount val="16"/>
                 <c:lvl>
                   <c:pt idx="0">
                     <c:v>disp</c:v>
@@ -1453,6 +1521,12 @@
                     <c:v>disp</c:v>
                   </c:pt>
                   <c:pt idx="13">
+                    <c:v>disp</c:v>
+                  </c:pt>
+                  <c:pt idx="14">
+                    <c:v>disp</c:v>
+                  </c:pt>
+                  <c:pt idx="15">
                     <c:v>disp</c:v>
                   </c:pt>
                 </c:lvl>
@@ -1466,14 +1540,14 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Folha1!$G$8:$G$35</c15:sqref>
+                    <c15:sqref>comJiji!$G$8:$G$39</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Folha1!$G$9,Folha1!$G$11,Folha1!$G$13,Folha1!$G$15,Folha1!$G$17,Folha1!$G$19,Folha1!$G$21,Folha1!$G$23,Folha1!$G$25,Folha1!$G$27,Folha1!$G$29,Folha1!$G$31,Folha1!$G$33,Folha1!$G$35)</c:f>
+              <c:f>(comJiji!$G$9,comJiji!$G$11,comJiji!$G$13,comJiji!$G$15,comJiji!$G$17,comJiji!$G$19,comJiji!$G$21,comJiji!$G$23,comJiji!$G$25,comJiji!$G$27,comJiji!$G$29,comJiji!$G$31,comJiji!$G$33,comJiji!$G$35,comJiji!$G$37,comJiji!$G$39)</c:f>
               <c:numCache>
                 <c:formatCode>0.00E+00</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>6E-10</c:v>
                 </c:pt>
@@ -1487,33 +1561,39 @@
                   <c:v>9.1099999999999996E-10</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>1.71E-10</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.8699999999999999E-11</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>6.4400000000000001E-9</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
                   <c:v>4.8499999999999996E-9</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="8">
                   <c:v>5.6299999999999998E-9</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="9">
                   <c:v>3.9700000000000001E-9</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="10">
                   <c:v>3.8200000000000003E-10</c:v>
                 </c:pt>
-                <c:pt idx="9">
-                  <c:v>5.2599999999999996E-9</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1.44E-9</c:v>
-                </c:pt>
                 <c:pt idx="11">
+                  <c:v>7.1699999999999998E-9</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.85E-9</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>2.7000000000000002E-9</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="14">
                   <c:v>1.38E-9</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="15">
                   <c:v>8.6399999999999999E-9</c:v>
                 </c:pt>
               </c:numCache>
@@ -1522,7 +1602,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-D2EE-42FB-9F04-031C26ED6FF5}"/>
+              <c16:uniqueId val="{00000000-407A-40F2-BEDD-F1A63840F746}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1531,7 +1611,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Folha1!$H$7</c:f>
+              <c:f>comJiji!$H$7</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1569,13 +1649,13 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Folha1!$D$8:$F$35</c15:sqref>
+                    <c15:sqref>comJiji!$D$8:$F$39</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Folha1!$D$9:$F$9,Folha1!$D$11:$F$11,Folha1!$D$13:$F$13,Folha1!$D$15:$F$15,Folha1!$D$17:$F$17,Folha1!$D$19:$F$19,Folha1!$D$21:$F$21,Folha1!$D$23:$F$23,Folha1!$D$25:$F$25,Folha1!$D$27:$F$27,Folha1!$D$29:$F$29,Folha1!$D$31:$F$31,Folha1!$D$33:$F$33,Folha1!$D$35:$F$35)</c:f>
+              <c:f>(comJiji!$D$9:$F$9,comJiji!$D$11:$F$11,comJiji!$D$13:$F$13,comJiji!$D$15:$F$15,comJiji!$D$17:$F$17,comJiji!$D$19:$F$19,comJiji!$D$21:$F$21,comJiji!$D$23:$F$23,comJiji!$D$25:$F$25,comJiji!$D$27:$F$27,comJiji!$D$29:$F$29,comJiji!$D$31:$F$31,comJiji!$D$33:$F$33,comJiji!$D$35:$F$35,comJiji!$D$37:$F$37,comJiji!$D$39:$F$39)</c:f>
               <c:multiLvlStrCache>
-                <c:ptCount val="14"/>
+                <c:ptCount val="16"/>
                 <c:lvl>
                   <c:pt idx="0">
                     <c:v>disp</c:v>
@@ -1617,6 +1697,12 @@
                     <c:v>disp</c:v>
                   </c:pt>
                   <c:pt idx="13">
+                    <c:v>disp</c:v>
+                  </c:pt>
+                  <c:pt idx="14">
+                    <c:v>disp</c:v>
+                  </c:pt>
+                  <c:pt idx="15">
                     <c:v>disp</c:v>
                   </c:pt>
                 </c:lvl>
@@ -1630,14 +1716,14 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Folha1!$H$8:$H$35</c15:sqref>
+                    <c15:sqref>comJiji!$H$8:$H$39</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Folha1!$H$9,Folha1!$H$11,Folha1!$H$13,Folha1!$H$15,Folha1!$H$17,Folha1!$H$19,Folha1!$H$21,Folha1!$H$23,Folha1!$H$25,Folha1!$H$27,Folha1!$H$29,Folha1!$H$31,Folha1!$H$33,Folha1!$H$35)</c:f>
+              <c:f>(comJiji!$H$9,comJiji!$H$11,comJiji!$H$13,comJiji!$H$15,comJiji!$H$17,comJiji!$H$19,comJiji!$H$21,comJiji!$H$23,comJiji!$H$25,comJiji!$H$27,comJiji!$H$29,comJiji!$H$31,comJiji!$H$33,comJiji!$H$35,comJiji!$H$37,comJiji!$H$39)</c:f>
               <c:numCache>
                 <c:formatCode>0.00E+00</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>1.5900000000000001E-12</c:v>
                 </c:pt>
@@ -1651,33 +1737,39 @@
                   <c:v>6.5600000000000003E-13</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>1.25E-14</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.6199999999999997E-15</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>8.4400000000000004E-13</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
                   <c:v>5.4200000000000001E-13</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="8">
                   <c:v>1.66E-12</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="9">
                   <c:v>2.2100000000000001E-12</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="10">
                   <c:v>2.4099999999999998E-13</c:v>
                 </c:pt>
-                <c:pt idx="9">
-                  <c:v>3.1399999999999999E-12</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>6.9799999999999995E-13</c:v>
-                </c:pt>
                 <c:pt idx="11">
+                  <c:v>4.7200000000000001E-12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.24E-12</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>9.3199999999999999E-12</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="14">
                   <c:v>1.9899999999999998E-12</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="15">
                   <c:v>1.7399999999999999E-11</c:v>
                 </c:pt>
               </c:numCache>
@@ -1686,7 +1778,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-D2EE-42FB-9F04-031C26ED6FF5}"/>
+              <c16:uniqueId val="{00000001-407A-40F2-BEDD-F1A63840F746}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1695,7 +1787,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Folha1!$I$7</c:f>
+              <c:f>comJiji!$I$7</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1733,13 +1825,13 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Folha1!$D$8:$F$35</c15:sqref>
+                    <c15:sqref>comJiji!$D$8:$F$39</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Folha1!$D$9:$F$9,Folha1!$D$11:$F$11,Folha1!$D$13:$F$13,Folha1!$D$15:$F$15,Folha1!$D$17:$F$17,Folha1!$D$19:$F$19,Folha1!$D$21:$F$21,Folha1!$D$23:$F$23,Folha1!$D$25:$F$25,Folha1!$D$27:$F$27,Folha1!$D$29:$F$29,Folha1!$D$31:$F$31,Folha1!$D$33:$F$33,Folha1!$D$35:$F$35)</c:f>
+              <c:f>(comJiji!$D$9:$F$9,comJiji!$D$11:$F$11,comJiji!$D$13:$F$13,comJiji!$D$15:$F$15,comJiji!$D$17:$F$17,comJiji!$D$19:$F$19,comJiji!$D$21:$F$21,comJiji!$D$23:$F$23,comJiji!$D$25:$F$25,comJiji!$D$27:$F$27,comJiji!$D$29:$F$29,comJiji!$D$31:$F$31,comJiji!$D$33:$F$33,comJiji!$D$35:$F$35,comJiji!$D$37:$F$37,comJiji!$D$39:$F$39)</c:f>
               <c:multiLvlStrCache>
-                <c:ptCount val="14"/>
+                <c:ptCount val="16"/>
                 <c:lvl>
                   <c:pt idx="0">
                     <c:v>disp</c:v>
@@ -1781,6 +1873,12 @@
                     <c:v>disp</c:v>
                   </c:pt>
                   <c:pt idx="13">
+                    <c:v>disp</c:v>
+                  </c:pt>
+                  <c:pt idx="14">
+                    <c:v>disp</c:v>
+                  </c:pt>
+                  <c:pt idx="15">
                     <c:v>disp</c:v>
                   </c:pt>
                 </c:lvl>
@@ -1794,14 +1892,14 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Folha1!$I$8:$I$35</c15:sqref>
+                    <c15:sqref>comJiji!$I$8:$I$39</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>(Folha1!$I$9,Folha1!$I$11,Folha1!$I$13,Folha1!$I$15,Folha1!$I$17,Folha1!$I$19,Folha1!$I$21,Folha1!$I$23,Folha1!$I$25,Folha1!$I$27,Folha1!$I$29,Folha1!$I$31,Folha1!$I$33,Folha1!$I$35)</c:f>
+              <c:f>(comJiji!$I$9,comJiji!$I$11,comJiji!$I$13,comJiji!$I$15,comJiji!$I$17,comJiji!$I$19,comJiji!$I$21,comJiji!$I$23,comJiji!$I$25,comJiji!$I$27,comJiji!$I$29,comJiji!$I$31,comJiji!$I$33,comJiji!$I$35,comJiji!$I$37,comJiji!$I$39)</c:f>
               <c:numCache>
                 <c:formatCode>0.00E+00</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>5.6800000000000002E-9</c:v>
                 </c:pt>
@@ -1815,33 +1913,39 @@
                   <c:v>6.1700000000000004E-11</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>2.5299999999999998E-5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.34E-5</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>1.3799999999999999E-8</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
                   <c:v>1.14E-8</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="8">
                   <c:v>1.4100000000000001E-8</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="9">
                   <c:v>1.4E-8</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="10">
                   <c:v>2.81E-9</c:v>
                 </c:pt>
-                <c:pt idx="9">
-                  <c:v>1.6499999999999999E-8</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>8.0299999999999998E-8</c:v>
-                </c:pt>
                 <c:pt idx="11">
+                  <c:v>2.1400000000000001E-10</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3.5000000000000002E-8</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>1.4E-8</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="14">
                   <c:v>5.1499999999999998E-9</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="15">
                   <c:v>1.4100000000000001E-8</c:v>
                 </c:pt>
               </c:numCache>
@@ -1850,7 +1954,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-D2EE-42FB-9F04-031C26ED6FF5}"/>
+              <c16:uniqueId val="{00000002-407A-40F2-BEDD-F1A63840F746}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1920,8 +2024,7 @@
         <c:scaling>
           <c:logBase val="10"/>
           <c:orientation val="minMax"/>
-          <c:max val="2.0000000000000008E-5"/>
-          <c:min val="2.0000000000000013E-13"/>
+          <c:max val="1.0000000000000003E-4"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -2206,6 +2309,2523 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
+              <c:f>comJiji!$G$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>PIDF</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>comJiji!$J$40:$J$45</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>média MSE Accel &amp; Disp</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>mediana MSE Accel &amp; Disp</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>média MSE Accel</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>mediana MSE Accel</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>média MSE Disp</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>mediana MSE Disp</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>comJiji!$G$40:$G$45</c:f>
+              <c:numCache>
+                <c:formatCode>0.00E+00</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2.7141214706156249E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.00432E-6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.42824E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.9199999999999999E-5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.9412312500000006E-9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.9150000000000001E-9</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8949-4F6F-B138-3C7885DF6E94}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>comJiji!$H$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Optimal Control</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>comJiji!$J$40:$J$45</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>média MSE Accel &amp; Disp</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>mediana MSE Accel &amp; Disp</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>média MSE Accel</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>mediana MSE Accel</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>média MSE Disp</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>mediana MSE Disp</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>comJiji!$H$40:$H$45</c:f>
+              <c:numCache>
+                <c:formatCode>0.00E+00</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1.4838187920687225E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.5158700000000001E-8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.9676375812499995E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.3149999999999999E-6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.8874450000000001E-12</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.5050000000000002E-12</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-8949-4F6F-B138-3C7885DF6E94}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>comJiji!$I$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Adapted Driver (3rd)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="00B0F0"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="00B0F0"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>comJiji!$J$40:$J$45</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>média MSE Accel &amp; Disp</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>mediana MSE Accel &amp; Disp</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>média MSE Accel</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>mediana MSE Accel</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>média MSE Disp</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>mediana MSE Disp</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>comJiji!$I$40:$I$45</c:f>
+              <c:numCache>
+                <c:formatCode>0.00E+00</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1.1439522328615623E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.3499999999999997E-6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.2876204375E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.205E-5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.8402822312499994E-6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.4E-8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-8949-4F6F-B138-3C7885DF6E94}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1230024880"/>
+        <c:axId val="1230026800"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1230024880"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-PT"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1230026800"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1230026800"/>
+        <c:scaling>
+          <c:logBase val="10"/>
+          <c:orientation val="minMax"/>
+          <c:max val="3.0000000000000006E-2"/>
+          <c:min val="1.0000000000000006E-12"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pt-PT" sz="1200">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Displacement</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="pt-PT" sz="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t> Response Spectrum MSE (m)</a:t>
+                </a:r>
+                <a:endParaRPr lang="pt-PT" sz="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:endParaRPr>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-PT"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.00E+00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-PT"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1230024880"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-PT"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-PT"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-PT"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-PT">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Acceleration</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="pt-PT" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t> response spectrum MSE vs control strategy for various seismic signals</a:t>
+            </a:r>
+            <a:endParaRPr lang="pt-PT">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-PT"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Folha1!$G$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>PIDF</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Folha1!$D$8:$F$35</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(Folha1!$D$8:$F$8,Folha1!$D$10:$F$10,Folha1!$D$12:$F$12,Folha1!$D$14:$F$14,Folha1!$D$16:$F$16,Folha1!$D$18:$F$18,Folha1!$D$20:$F$20,Folha1!$D$22:$F$22,Folha1!$D$24:$F$24,Folha1!$D$26:$F$26,Folha1!$D$28:$F$28,Folha1!$D$30:$F$30,Folha1!$D$32:$F$32,Folha1!$D$34:$F$34)</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="14"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>acc</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>acc</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>acc</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>acc</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>acc</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>acc</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>acc</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>acc</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>acc</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>acc</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>acc</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>acc</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>acc</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>acc</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>N</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>P</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>N</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>P</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>N</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>P</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>N</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>N</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>P</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>N</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>P</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>N</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>P</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>N</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>El Centro</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Erzikan</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Kobe</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>L'Aquila</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Newhall</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Rinaldi</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Sylmar</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Tolmezzo</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Folha1!$G$8:$G$35</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(Folha1!$G$8,Folha1!$G$10,Folha1!$G$12,Folha1!$G$14,Folha1!$G$16,Folha1!$G$18,Folha1!$G$20,Folha1!$G$22,Folha1!$G$24,Folha1!$G$26,Folha1!$G$28,Folha1!$G$30,Folha1!$G$32,Folha1!$G$34)</c:f>
+              <c:numCache>
+                <c:formatCode>0.00E+00</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>5.6199999999999997E-5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.3200000000000001E-5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.9999999999999999E-6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.1099999999999996E-6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.1000000000000001E-5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.09E-5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.98E-5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.34E-5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6.7499999999999997E-6</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.8E-5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5.8900000000000002E-5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.8600000000000001E-5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4.9799999999999998E-6</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3.0400000000000002E-4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-DA05-4E58-AC06-AF98CDCBEC7D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Folha1!$H$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Optimal Control</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="FFC000"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Folha1!$D$8:$F$35</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(Folha1!$D$8:$F$8,Folha1!$D$10:$F$10,Folha1!$D$12:$F$12,Folha1!$D$14:$F$14,Folha1!$D$16:$F$16,Folha1!$D$18:$F$18,Folha1!$D$20:$F$20,Folha1!$D$22:$F$22,Folha1!$D$24:$F$24,Folha1!$D$26:$F$26,Folha1!$D$28:$F$28,Folha1!$D$30:$F$30,Folha1!$D$32:$F$32,Folha1!$D$34:$F$34)</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="14"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>acc</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>acc</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>acc</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>acc</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>acc</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>acc</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>acc</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>acc</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>acc</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>acc</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>acc</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>acc</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>acc</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>acc</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>N</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>P</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>N</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>P</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>N</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>P</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>N</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>N</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>P</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>N</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>P</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>N</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>P</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>N</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>El Centro</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Erzikan</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Kobe</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>L'Aquila</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Newhall</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Rinaldi</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Sylmar</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Tolmezzo</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Folha1!$H$8:$H$35</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(Folha1!$H$8,Folha1!$H$10,Folha1!$H$12,Folha1!$H$14,Folha1!$H$16,Folha1!$H$18,Folha1!$H$20,Folha1!$H$22,Folha1!$H$24,Folha1!$H$26,Folha1!$H$28,Folha1!$H$30,Folha1!$H$32,Folha1!$H$34)</c:f>
+              <c:numCache>
+                <c:formatCode>0.00E+00</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>1.11E-5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.0199999999999999E-6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.8299999999999998E-7</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.0300000000000001E-8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.0800000000000001E-7</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.19E-6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.1199999999999998E-7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8.8800000000000001E-7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.61E-6</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.91E-5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4.32E-5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3.0900000000000001E-6</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4.3000000000000001E-7</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>8.7399999999999997E-5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-DA05-4E58-AC06-AF98CDCBEC7D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Folha1!$I$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Adapted Driver (3rd)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="00B0F0"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="00B0F0"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Folha1!$D$8:$F$35</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(Folha1!$D$8:$F$8,Folha1!$D$10:$F$10,Folha1!$D$12:$F$12,Folha1!$D$14:$F$14,Folha1!$D$16:$F$16,Folha1!$D$18:$F$18,Folha1!$D$20:$F$20,Folha1!$D$22:$F$22,Folha1!$D$24:$F$24,Folha1!$D$26:$F$26,Folha1!$D$28:$F$28,Folha1!$D$30:$F$30,Folha1!$D$32:$F$32,Folha1!$D$34:$F$34)</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="14"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>acc</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>acc</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>acc</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>acc</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>acc</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>acc</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>acc</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>acc</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>acc</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>acc</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>acc</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>acc</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>acc</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>acc</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>N</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>P</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>N</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>P</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>N</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>P</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>N</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>N</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>P</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>N</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>P</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>N</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>P</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>N</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>El Centro</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Erzikan</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Kobe</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>L'Aquila</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Newhall</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Rinaldi</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Sylmar</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Tolmezzo</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Folha1!$I$8:$I$35</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(Folha1!$I$8,Folha1!$I$10,Folha1!$I$12,Folha1!$I$14,Folha1!$I$16,Folha1!$I$18,Folha1!$I$20,Folha1!$I$22,Folha1!$I$24,Folha1!$I$26,Folha1!$I$28,Folha1!$I$30,Folha1!$I$32,Folha1!$I$34)</c:f>
+              <c:numCache>
+                <c:formatCode>0.00E+00</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>4.9100000000000001E-5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.5999999999999996E-6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.76E-6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.0999999999999998E-6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.9000000000000001E-5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.7099999999999999E-5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.0200000000000001E-5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.4399999999999999E-5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.51E-5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.8999999999999999E-5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>6.4999999999999994E-5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5.0099999999999998E-5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>9.8099999999999992E-6</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.67E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-DA05-4E58-AC06-AF98CDCBEC7D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1230024880"/>
+        <c:axId val="1230026800"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1230024880"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-PT"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1230026800"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1230026800"/>
+        <c:scaling>
+          <c:logBase val="10"/>
+          <c:orientation val="minMax"/>
+          <c:max val="2.0000000000000005E-3"/>
+          <c:min val="7.0000000000000031E-8"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pt-PT" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Acceleration Response Spectrum MSE (m/s^2)</a:t>
+                </a:r>
+                <a:endParaRPr lang="pt-PT" sz="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:endParaRPr>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-PT"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.00E+00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-PT"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1230024880"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-PT"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-PT"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-PT"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-PT" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Displacement response spectrum MSE vs control strategy for various seismic signals</a:t>
+            </a:r>
+            <a:endParaRPr lang="pt-PT">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-PT"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Folha1!$G$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>PIDF</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Folha1!$D$8:$F$35</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(Folha1!$D$9:$F$9,Folha1!$D$11:$F$11,Folha1!$D$13:$F$13,Folha1!$D$15:$F$15,Folha1!$D$17:$F$17,Folha1!$D$19:$F$19,Folha1!$D$21:$F$21,Folha1!$D$23:$F$23,Folha1!$D$25:$F$25,Folha1!$D$27:$F$27,Folha1!$D$29:$F$29,Folha1!$D$31:$F$31,Folha1!$D$33:$F$33,Folha1!$D$35:$F$35)</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="14"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>disp</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>disp</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>disp</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>disp</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>disp</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>disp</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>disp</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>disp</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>disp</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>disp</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>disp</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>disp</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>disp</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>disp</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl/>
+                <c:lvl/>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Folha1!$G$8:$G$35</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(Folha1!$G$9,Folha1!$G$11,Folha1!$G$13,Folha1!$G$15,Folha1!$G$17,Folha1!$G$19,Folha1!$G$21,Folha1!$G$23,Folha1!$G$25,Folha1!$G$27,Folha1!$G$29,Folha1!$G$31,Folha1!$G$33,Folha1!$G$35)</c:f>
+              <c:numCache>
+                <c:formatCode>0.00E+00</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>6E-10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.4699999999999999E-10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.9800000000000002E-9</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.1099999999999996E-10</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.4400000000000001E-9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.8499999999999996E-9</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.6299999999999998E-9</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.9700000000000001E-9</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.8200000000000003E-10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7.1699999999999998E-9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.85E-9</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.7000000000000002E-9</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.38E-9</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>8.6399999999999999E-9</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D2EE-42FB-9F04-031C26ED6FF5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Folha1!$H$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Optimal Control</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="FFC000"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Folha1!$D$8:$F$35</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(Folha1!$D$9:$F$9,Folha1!$D$11:$F$11,Folha1!$D$13:$F$13,Folha1!$D$15:$F$15,Folha1!$D$17:$F$17,Folha1!$D$19:$F$19,Folha1!$D$21:$F$21,Folha1!$D$23:$F$23,Folha1!$D$25:$F$25,Folha1!$D$27:$F$27,Folha1!$D$29:$F$29,Folha1!$D$31:$F$31,Folha1!$D$33:$F$33,Folha1!$D$35:$F$35)</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="14"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>disp</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>disp</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>disp</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>disp</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>disp</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>disp</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>disp</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>disp</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>disp</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>disp</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>disp</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>disp</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>disp</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>disp</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl/>
+                <c:lvl/>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Folha1!$H$8:$H$35</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(Folha1!$H$9,Folha1!$H$11,Folha1!$H$13,Folha1!$H$15,Folha1!$H$17,Folha1!$H$19,Folha1!$H$21,Folha1!$H$23,Folha1!$H$25,Folha1!$H$27,Folha1!$H$29,Folha1!$H$31,Folha1!$H$33,Folha1!$H$35)</c:f>
+              <c:numCache>
+                <c:formatCode>0.00E+00</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>1.5900000000000001E-12</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.3499999999999999E-12</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.42E-12</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.5600000000000003E-13</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8.4400000000000004E-13</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.4200000000000001E-13</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.66E-12</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.2100000000000001E-12</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.4099999999999998E-13</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4.7200000000000001E-12</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.24E-12</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>9.3199999999999999E-12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.9899999999999998E-12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.7399999999999999E-11</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-D2EE-42FB-9F04-031C26ED6FF5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Folha1!$I$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Adapted Driver (3rd)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="00B0F0"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="00B0F0"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Folha1!$D$8:$F$35</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(Folha1!$D$9:$F$9,Folha1!$D$11:$F$11,Folha1!$D$13:$F$13,Folha1!$D$15:$F$15,Folha1!$D$17:$F$17,Folha1!$D$19:$F$19,Folha1!$D$21:$F$21,Folha1!$D$23:$F$23,Folha1!$D$25:$F$25,Folha1!$D$27:$F$27,Folha1!$D$29:$F$29,Folha1!$D$31:$F$31,Folha1!$D$33:$F$33,Folha1!$D$35:$F$35)</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="14"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>disp</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>disp</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>disp</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>disp</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>disp</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>disp</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>disp</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>disp</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>disp</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>disp</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>disp</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>disp</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>disp</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>disp</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl/>
+                <c:lvl/>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Folha1!$I$8:$I$35</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(Folha1!$I$9,Folha1!$I$11,Folha1!$I$13,Folha1!$I$15,Folha1!$I$17,Folha1!$I$19,Folha1!$I$21,Folha1!$I$23,Folha1!$I$25,Folha1!$I$27,Folha1!$I$29,Folha1!$I$31,Folha1!$I$33,Folha1!$I$35)</c:f>
+              <c:numCache>
+                <c:formatCode>0.00E+00</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>5.6800000000000002E-9</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.42E-8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.6000000000000003E-6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.1700000000000004E-11</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.3799999999999999E-8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.14E-8</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.4100000000000001E-8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.4E-8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.81E-9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.1400000000000001E-10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3.5000000000000002E-8</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.4E-8</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>5.1499999999999998E-9</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.4100000000000001E-8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-D2EE-42FB-9F04-031C26ED6FF5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1230024880"/>
+        <c:axId val="1230026800"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1230024880"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-PT"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1230026800"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1230026800"/>
+        <c:scaling>
+          <c:logBase val="10"/>
+          <c:orientation val="minMax"/>
+          <c:max val="2.0000000000000008E-5"/>
+          <c:min val="2.0000000000000013E-13"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pt-PT" sz="1200">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Displacement</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="pt-PT" sz="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t> Response Spectrum MSE (m)</a:t>
+                </a:r>
+                <a:endParaRPr lang="pt-PT" sz="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:endParaRPr>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-PT"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.00E+00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-PT"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1230024880"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-PT"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-PT"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-PT"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-PT" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Mean &amp; Average Statistics for all seismic signals</a:t>
+            </a:r>
+            <a:endParaRPr lang="pt-PT">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-PT"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
               <c:f>Folha1!$G$7</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
@@ -2270,19 +4890,19 @@
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>1.8831590357142854E-5</c:v>
+                  <c:v>2.0424530357142859E-5</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>1.00432E-6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.7660000000000002E-5</c:v>
+                  <c:v>4.0845714285714295E-5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.6000000000000003E-5</c:v>
+                  <c:v>1.8300000000000001E-5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.180714285714286E-9</c:v>
+                  <c:v>3.3464285714285716E-9</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>2.3400000000000002E-9</c:v>
@@ -2293,7 +4913,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-EF3B-42BA-9EFD-08D9A66046A6}"/>
+              <c16:uniqueId val="{00000000-891B-4A6C-9D50-0D1FB550CE3F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2366,19 +4986,19 @@
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>1.1470762287892856E-5</c:v>
+                  <c:v>6.1500480779642854E-6</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>3.5158700000000001E-8</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.2941521428571429E-5</c:v>
+                  <c:v>1.2300092857142856E-5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.235E-6</c:v>
+                  <c:v>1.4000000000000001E-6</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.1472142857142858E-12</c:v>
+                  <c:v>3.2987857142857144E-12</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>1.625E-12</c:v>
@@ -2389,7 +5009,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-EF3B-42BA-9EFD-08D9A66046A6}"/>
+              <c16:uniqueId val="{00000001-891B-4A6C-9D50-0D1FB550CE3F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2462,22 +5082,22 @@
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>7.9763432203571423E-5</c:v>
+                  <c:v>7.2357661275000007E-5</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>5.1800000000000004E-6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.5904071428571426E-4</c:v>
+                  <c:v>1.4423357142857144E-4</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>2.2050000000000001E-5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.8615012142857137E-7</c:v>
+                  <c:v>4.8175112142857149E-7</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.4E-8</c:v>
+                  <c:v>1.3899999999999999E-8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2485,7 +5105,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-EF3B-42BA-9EFD-08D9A66046A6}"/>
+              <c16:uniqueId val="{00000002-891B-4A6C-9D50-0D1FB550CE3F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2872,6 +5492,126 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
@@ -4420,7 +7160,1674 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>247649</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>211666</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4DD6365B-2CC4-4D3F-BBF5-0F55C152FF8A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>239448</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>75407</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>207698</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>11906</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Gráfico 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{145BAD1E-03E1-452C-9217-A2CB533A727F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>323941</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>165636</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="13" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DAE1E80C-8D0A-4CB1-8F95-09369CDFF122}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -4499,28 +8906,26 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>457291</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>117988</xdr:rowOff>
+      <xdr:colOff>549468</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>148714</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>102576</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>43962</xdr:rowOff>
+      <xdr:colOff>194753</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>74689</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Gráfico 1">
+        <xdr:cNvPr id="3" name="Gráfico 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{859274BD-7D23-4341-821E-9C7CF27A40C7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FAAA406C-3B13-A42E-7F0B-C7434FC6DCE0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
+        <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -4853,6 +9258,743 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{225F96D6-ED0D-45B4-865A-35F865CA620B}">
+  <dimension ref="D7:J46"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="9" width="9.140625" style="1"/>
+    <col min="10" max="10" width="24.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="7" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="G7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="D8" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G8" s="2">
+        <v>5.6199999999999997E-5</v>
+      </c>
+      <c r="H8" s="2">
+        <v>1.11E-5</v>
+      </c>
+      <c r="I8" s="2">
+        <v>4.9100000000000001E-5</v>
+      </c>
+    </row>
+    <row r="9" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G9" s="2">
+        <v>6E-10</v>
+      </c>
+      <c r="H9" s="2">
+        <v>1.5900000000000001E-12</v>
+      </c>
+      <c r="I9" s="2">
+        <v>5.6800000000000002E-9</v>
+      </c>
+      <c r="J9" s="16"/>
+    </row>
+    <row r="10" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="D10" s="15"/>
+      <c r="E10" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G10" s="2">
+        <v>1.3200000000000001E-5</v>
+      </c>
+      <c r="H10" s="2">
+        <v>3.0199999999999999E-6</v>
+      </c>
+      <c r="I10" s="2">
+        <v>9.5999999999999996E-6</v>
+      </c>
+      <c r="J10" s="16"/>
+    </row>
+    <row r="11" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G11" s="2">
+        <v>3.4699999999999999E-10</v>
+      </c>
+      <c r="H11" s="2">
+        <v>2.3499999999999999E-12</v>
+      </c>
+      <c r="I11" s="2">
+        <v>1.42E-8</v>
+      </c>
+      <c r="J11" s="17"/>
+    </row>
+    <row r="12" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="D12" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G12" s="2">
+        <v>1.9999999999999999E-6</v>
+      </c>
+      <c r="H12" s="2">
+        <v>3.8299999999999998E-7</v>
+      </c>
+      <c r="I12" s="2">
+        <v>3.76E-6</v>
+      </c>
+      <c r="J12" s="17"/>
+    </row>
+    <row r="13" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G13" s="2">
+        <v>1.9800000000000002E-9</v>
+      </c>
+      <c r="H13" s="2">
+        <v>1.42E-12</v>
+      </c>
+      <c r="I13" s="2">
+        <v>6.6000000000000003E-6</v>
+      </c>
+      <c r="J13" s="17"/>
+    </row>
+    <row r="14" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="D14" s="15"/>
+      <c r="E14" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G14" s="2">
+        <v>4.1099999999999996E-6</v>
+      </c>
+      <c r="H14" s="2">
+        <v>7.0300000000000001E-8</v>
+      </c>
+      <c r="I14" s="2">
+        <v>7.0999999999999998E-6</v>
+      </c>
+      <c r="J14" s="17"/>
+    </row>
+    <row r="15" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G15" s="2">
+        <v>9.1099999999999996E-10</v>
+      </c>
+      <c r="H15" s="2">
+        <v>6.5600000000000003E-13</v>
+      </c>
+      <c r="I15" s="2">
+        <v>6.1700000000000004E-11</v>
+      </c>
+      <c r="J15" s="17"/>
+    </row>
+    <row r="16" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="D16" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G16" s="2">
+        <v>4.28E-3</v>
+      </c>
+      <c r="H16" s="2">
+        <v>2.2100000000000002E-3</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0.17499999999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G17" s="2">
+        <v>1.71E-10</v>
+      </c>
+      <c r="H17" s="2">
+        <v>1.25E-14</v>
+      </c>
+      <c r="I17" s="2">
+        <v>2.5299999999999998E-5</v>
+      </c>
+    </row>
+    <row r="18" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D18" s="15"/>
+      <c r="E18" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G18" s="2">
+        <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="H18" s="2">
+        <v>4.5100000000000001E-2</v>
+      </c>
+      <c r="I18" s="2">
+        <v>0.189</v>
+      </c>
+    </row>
+    <row r="19" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G19" s="2">
+        <v>3.8699999999999999E-11</v>
+      </c>
+      <c r="H19" s="2">
+        <v>3.6199999999999997E-15</v>
+      </c>
+      <c r="I19" s="2">
+        <v>1.34E-5</v>
+      </c>
+    </row>
+    <row r="20" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D20" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G20" s="2">
+        <v>3.1000000000000001E-5</v>
+      </c>
+      <c r="H20" s="2">
+        <v>3.0800000000000001E-7</v>
+      </c>
+      <c r="I20" s="2">
+        <v>1.9000000000000001E-5</v>
+      </c>
+    </row>
+    <row r="21" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G21" s="2">
+        <v>6.4400000000000001E-9</v>
+      </c>
+      <c r="H21" s="2">
+        <v>8.4400000000000004E-13</v>
+      </c>
+      <c r="I21" s="2">
+        <v>1.3799999999999999E-8</v>
+      </c>
+    </row>
+    <row r="22" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D22" s="15"/>
+      <c r="E22" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G22" s="2">
+        <v>2.09E-5</v>
+      </c>
+      <c r="H22" s="2">
+        <v>1.19E-6</v>
+      </c>
+      <c r="I22" s="2">
+        <v>1.7099999999999999E-5</v>
+      </c>
+    </row>
+    <row r="23" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G23" s="2">
+        <v>4.8499999999999996E-9</v>
+      </c>
+      <c r="H23" s="2">
+        <v>5.4200000000000001E-13</v>
+      </c>
+      <c r="I23" s="2">
+        <v>1.14E-8</v>
+      </c>
+    </row>
+    <row r="24" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D24" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G24" s="2">
+        <v>1.98E-5</v>
+      </c>
+      <c r="H24" s="2">
+        <v>4.1199999999999998E-7</v>
+      </c>
+      <c r="I24" s="2">
+        <v>4.0200000000000001E-5</v>
+      </c>
+    </row>
+    <row r="25" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G25" s="2">
+        <v>5.6299999999999998E-9</v>
+      </c>
+      <c r="H25" s="2">
+        <v>1.66E-12</v>
+      </c>
+      <c r="I25" s="2">
+        <v>1.4100000000000001E-8</v>
+      </c>
+    </row>
+    <row r="26" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D26" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G26" s="2">
+        <v>1.34E-5</v>
+      </c>
+      <c r="H26" s="2">
+        <v>8.8800000000000001E-7</v>
+      </c>
+      <c r="I26" s="2">
+        <v>1.4399999999999999E-5</v>
+      </c>
+    </row>
+    <row r="27" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G27" s="2">
+        <v>3.9700000000000001E-9</v>
+      </c>
+      <c r="H27" s="2">
+        <v>2.2100000000000001E-12</v>
+      </c>
+      <c r="I27" s="2">
+        <v>1.4E-8</v>
+      </c>
+    </row>
+    <row r="28" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D28" s="15"/>
+      <c r="E28" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G28" s="2">
+        <v>6.7499999999999997E-6</v>
+      </c>
+      <c r="H28" s="2">
+        <v>1.61E-6</v>
+      </c>
+      <c r="I28" s="2">
+        <v>2.51E-5</v>
+      </c>
+    </row>
+    <row r="29" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G29" s="2">
+        <v>3.8200000000000003E-10</v>
+      </c>
+      <c r="H29" s="2">
+        <v>2.4099999999999998E-13</v>
+      </c>
+      <c r="I29" s="2">
+        <v>2.81E-9</v>
+      </c>
+    </row>
+    <row r="30" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D30" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E30" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G30" s="2">
+        <v>1.8E-5</v>
+      </c>
+      <c r="H30" s="2">
+        <v>1.91E-5</v>
+      </c>
+      <c r="I30" s="2">
+        <v>3.8999999999999999E-5</v>
+      </c>
+    </row>
+    <row r="31" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G31" s="2">
+        <v>7.1699999999999998E-9</v>
+      </c>
+      <c r="H31" s="2">
+        <v>4.7200000000000001E-12</v>
+      </c>
+      <c r="I31" s="2">
+        <v>2.1400000000000001E-10</v>
+      </c>
+    </row>
+    <row r="32" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D32" s="15"/>
+      <c r="E32" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G32" s="2">
+        <v>5.8900000000000002E-5</v>
+      </c>
+      <c r="H32" s="2">
+        <v>4.32E-5</v>
+      </c>
+      <c r="I32" s="2">
+        <v>6.4999999999999994E-5</v>
+      </c>
+    </row>
+    <row r="33" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G33" s="2">
+        <v>1.85E-9</v>
+      </c>
+      <c r="H33" s="2">
+        <v>1.24E-12</v>
+      </c>
+      <c r="I33" s="2">
+        <v>3.5000000000000002E-8</v>
+      </c>
+    </row>
+    <row r="34" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="D34" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G34" s="2">
+        <v>1.8600000000000001E-5</v>
+      </c>
+      <c r="H34" s="2">
+        <v>3.0900000000000001E-6</v>
+      </c>
+      <c r="I34" s="2">
+        <v>5.0099999999999998E-5</v>
+      </c>
+    </row>
+    <row r="35" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="D35" s="15"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G35" s="2">
+        <v>2.7000000000000002E-9</v>
+      </c>
+      <c r="H35" s="2">
+        <v>9.3199999999999999E-12</v>
+      </c>
+      <c r="I35" s="2">
+        <v>1.4E-8</v>
+      </c>
+    </row>
+    <row r="36" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="D36" s="15"/>
+      <c r="E36" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G36" s="2">
+        <v>4.9799999999999998E-6</v>
+      </c>
+      <c r="H36" s="2">
+        <v>4.3000000000000001E-7</v>
+      </c>
+      <c r="I36" s="2">
+        <v>9.8099999999999992E-6</v>
+      </c>
+    </row>
+    <row r="37" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="D37" s="15"/>
+      <c r="E37" s="15"/>
+      <c r="F37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G37" s="2">
+        <v>1.38E-9</v>
+      </c>
+      <c r="H37" s="2">
+        <v>1.9899999999999998E-12</v>
+      </c>
+      <c r="I37" s="2">
+        <v>5.1499999999999998E-9</v>
+      </c>
+    </row>
+    <row r="38" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="D38" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G38" s="2">
+        <v>3.0400000000000002E-4</v>
+      </c>
+      <c r="H38" s="2">
+        <v>8.7399999999999997E-5</v>
+      </c>
+      <c r="I38" s="2">
+        <v>1.67E-3</v>
+      </c>
+    </row>
+    <row r="39" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="D39" s="15"/>
+      <c r="E39" s="15"/>
+      <c r="F39" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G39" s="2">
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="H39" s="2">
+        <v>1.7399999999999999E-11</v>
+      </c>
+      <c r="I39" s="2">
+        <v>1.4100000000000001E-8</v>
+      </c>
+    </row>
+    <row r="40" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="G40" s="3">
+        <f>AVERAGE(G8:G39)</f>
+        <v>2.7141214706156249E-3</v>
+      </c>
+      <c r="H40" s="3">
+        <f>AVERAGE(H8:H39)</f>
+        <v>1.4838187920687225E-3</v>
+      </c>
+      <c r="I40" s="3">
+        <f>AVERAGE(I8:I39)</f>
+        <v>1.1439522328615623E-2</v>
+      </c>
+      <c r="J40" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="G41" s="5">
+        <f>MEDIAN(G8:G39)</f>
+        <v>1.00432E-6</v>
+      </c>
+      <c r="H41" s="5">
+        <f>MEDIAN(H8:H39)</f>
+        <v>3.5158700000000001E-8</v>
+      </c>
+      <c r="I41" s="5">
+        <f>MEDIAN(I8:I39)</f>
+        <v>8.3499999999999997E-6</v>
+      </c>
+      <c r="J41" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="F42" s="7"/>
+      <c r="G42" s="8">
+        <f>AVERAGE(G8,G10,G12,G14,G16,G18,G20,G22,G24,G26,G28,G30,G32,G34,G36,G38)</f>
+        <v>5.42824E-3</v>
+      </c>
+      <c r="H42" s="8">
+        <f>AVERAGE(H8,H10,H12,H14,H16,H18,H20,H22,H24,H26,H28,H30,H32,H34,H36,H38)</f>
+        <v>2.9676375812499995E-3</v>
+      </c>
+      <c r="I42" s="8">
+        <f>AVERAGE(I8,I10,I12,I14,I16,I18,I20,I22,I24,I26,I28,I30,I32,I34,I36,I38)</f>
+        <v>2.2876204375E-2</v>
+      </c>
+      <c r="J42" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="F43" s="7"/>
+      <c r="G43" s="8">
+        <f>MEDIAN(G8,G10,G12,G14,G16,G18,G20,G22,G24,G26,G28,G30,G32,G34,G36,G38)</f>
+        <v>1.9199999999999999E-5</v>
+      </c>
+      <c r="H43" s="8">
+        <f>MEDIAN(H8,H10,H12,H14,H16,H18,H20,H22,H24,H26,H28,H30,H32,H34,H36,H38)</f>
+        <v>2.3149999999999999E-6</v>
+      </c>
+      <c r="I43" s="8">
+        <f>MEDIAN(I8,I10,I12,I14,I16,I18,I20,I22,I24,I26,I28,I30,I32,I34,I36,I38)</f>
+        <v>3.205E-5</v>
+      </c>
+      <c r="J43" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="44" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="G44" s="10">
+        <f>AVERAGE(G9,G11,G13,G15,G17,G19,G21,G23,G25,G27,G29,G31,G33,G35,G37,G39)</f>
+        <v>2.9412312500000006E-9</v>
+      </c>
+      <c r="H44" s="10">
+        <f>AVERAGE(H9,H11,H13,H15,H17,H19,H21,H23,H25,H27,H29,H31,H33,H35,H37,H39)</f>
+        <v>2.8874450000000001E-12</v>
+      </c>
+      <c r="I44" s="10">
+        <f>AVERAGE(I9,I11,I13,I15,I17,I19,I21,I23,I25,I27,I29,I31,I33,I35,I37,I39)</f>
+        <v>2.8402822312499994E-6</v>
+      </c>
+      <c r="J44" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="45" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="G45" s="8">
+        <f>MEDIAN(G9,G11,G13,G15,G17,G19,G21,G23,G25,G27,G29,G31,G33,G35,G37,G39)</f>
+        <v>1.9150000000000001E-9</v>
+      </c>
+      <c r="H45" s="8">
+        <f>MEDIAN(H9,H11,H13,H15,H17,H19,H21,H23,H25,H27,H29,H31,H33,H35,H37,H39)</f>
+        <v>1.5050000000000002E-12</v>
+      </c>
+      <c r="I45" s="8">
+        <f>MEDIAN(I9,I11,I13,I15,I17,I19,I21,I23,I25,I27,I29,I31,I33,I35,I37,I39)</f>
+        <v>1.4E-8</v>
+      </c>
+      <c r="J45" s="11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="46" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="G46" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="H46" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I46" s="14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="25">
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="D26:D29"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="D16:D19"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="D30:D33"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="D34:D37"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="D20:D23"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="D8:D11"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="D12:D15"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="E14:E15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E6F0F66-B73B-4024-8B3D-E85F6FE3C626}">
   <dimension ref="D7:J42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5199,13 +10341,13 @@
         <v>2</v>
       </c>
       <c r="G26" s="2">
-        <v>1.2999999999999999E-5</v>
+        <v>1.8E-5</v>
       </c>
       <c r="H26" s="2">
-        <v>1.28E-6</v>
+        <v>1.91E-5</v>
       </c>
       <c r="I26" s="2">
-        <v>3.1300000000000002E-5</v>
+        <v>3.8999999999999999E-5</v>
       </c>
     </row>
     <row r="27" spans="4:9" x14ac:dyDescent="0.25">
@@ -5215,13 +10357,13 @@
         <v>3</v>
       </c>
       <c r="G27" s="2">
-        <v>5.2599999999999996E-9</v>
+        <v>7.1699999999999998E-9</v>
       </c>
       <c r="H27" s="2">
-        <v>3.1399999999999999E-12</v>
+        <v>4.7200000000000001E-12</v>
       </c>
       <c r="I27" s="2">
-        <v>1.6499999999999999E-8</v>
+        <v>2.1400000000000001E-10</v>
       </c>
     </row>
     <row r="28" spans="4:9" x14ac:dyDescent="0.25">
@@ -5233,13 +10375,13 @@
         <v>2</v>
       </c>
       <c r="G28" s="2">
-        <v>1.9300000000000002E-5</v>
+        <v>5.8900000000000002E-5</v>
       </c>
       <c r="H28" s="2">
-        <v>2.1000000000000001E-4</v>
+        <v>4.32E-5</v>
       </c>
       <c r="I28" s="2">
-        <v>2.7999999999999998E-4</v>
+        <v>6.4999999999999994E-5</v>
       </c>
     </row>
     <row r="29" spans="4:9" x14ac:dyDescent="0.25">
@@ -5249,13 +10391,13 @@
         <v>3</v>
       </c>
       <c r="G29" s="2">
-        <v>1.44E-9</v>
+        <v>1.85E-9</v>
       </c>
       <c r="H29" s="2">
-        <v>6.9799999999999995E-13</v>
+        <v>1.24E-12</v>
       </c>
       <c r="I29" s="2">
-        <v>8.0299999999999998E-8</v>
+        <v>3.5000000000000002E-8</v>
       </c>
     </row>
     <row r="30" spans="4:9" x14ac:dyDescent="0.25">
@@ -5367,15 +10509,15 @@
     <row r="36" spans="4:10" x14ac:dyDescent="0.25">
       <c r="G36" s="3">
         <f>AVERAGE(G8:G35)</f>
-        <v>1.8831590357142854E-5</v>
+        <v>2.0424530357142859E-5</v>
       </c>
       <c r="H36" s="3">
         <f>AVERAGE(H8:H35)</f>
-        <v>1.1470762287892856E-5</v>
+        <v>6.1500480779642854E-6</v>
       </c>
       <c r="I36" s="3">
         <f>AVERAGE(I8:I35)</f>
-        <v>7.9763432203571423E-5</v>
+        <v>7.2357661275000007E-5</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>16</v>
@@ -5402,15 +10544,15 @@
       <c r="F38" s="7"/>
       <c r="G38" s="8">
         <f>AVERAGE(G8,G10,G12,G14,G16,G18,G20,G22,G24,G26,G28,G30,G32,G34)</f>
-        <v>3.7660000000000002E-5</v>
+        <v>4.0845714285714295E-5</v>
       </c>
       <c r="H38" s="8">
-        <f t="shared" ref="H38:I38" si="0">AVERAGE(H8,H10,H12,H14,H16,H18,H20,H22,H24,H26,H28,H30,H32,H34)</f>
-        <v>2.2941521428571429E-5</v>
+        <f>AVERAGE(H8,H10,H12,H14,H16,H18,H20,H22,H24,H26,H28,H30,H32,H34)</f>
+        <v>1.2300092857142856E-5</v>
       </c>
       <c r="I38" s="8">
-        <f t="shared" si="0"/>
-        <v>1.5904071428571426E-4</v>
+        <f>AVERAGE(I8,I10,I12,I14,I16,I18,I20,I22,I24,I26,I28,I30,I32,I34)</f>
+        <v>1.4423357142857144E-4</v>
       </c>
       <c r="J38" s="9" t="s">
         <v>18</v>
@@ -5420,14 +10562,14 @@
       <c r="F39" s="7"/>
       <c r="G39" s="8">
         <f>MEDIAN(G8,G10,G12,G14,G16,G18,G20,G22,G24,G26,G28,G30,G32,G34)</f>
-        <v>1.6000000000000003E-5</v>
+        <v>1.8300000000000001E-5</v>
       </c>
       <c r="H39" s="8">
-        <f t="shared" ref="H39:I39" si="1">MEDIAN(H8,H10,H12,H14,H16,H18,H20,H22,H24,H26,H28,H30,H32,H34)</f>
-        <v>1.235E-6</v>
+        <f>MEDIAN(H8,H10,H12,H14,H16,H18,H20,H22,H24,H26,H28,H30,H32,H34)</f>
+        <v>1.4000000000000001E-6</v>
       </c>
       <c r="I39" s="8">
-        <f t="shared" si="1"/>
+        <f>MEDIAN(I8,I10,I12,I14,I16,I18,I20,I22,I24,I26,I28,I30,I32,I34)</f>
         <v>2.2050000000000001E-5</v>
       </c>
       <c r="J39" s="6" t="s">
@@ -5437,15 +10579,15 @@
     <row r="40" spans="4:10" x14ac:dyDescent="0.25">
       <c r="G40" s="10">
         <f>AVERAGE(G9,G11,G13,G15,G17,G19,G21,G23,G25,G27,G29,G31,G33,G35)</f>
-        <v>3.180714285714286E-9</v>
+        <v>3.3464285714285716E-9</v>
       </c>
       <c r="H40" s="10">
-        <f t="shared" ref="H40:I40" si="2">AVERAGE(H9,H11,H13,H15,H17,H19,H21,H23,H25,H27,H29,H31,H33,H35)</f>
-        <v>3.1472142857142858E-12</v>
+        <f>AVERAGE(H9,H11,H13,H15,H17,H19,H21,H23,H25,H27,H29,H31,H33,H35)</f>
+        <v>3.2987857142857144E-12</v>
       </c>
       <c r="I40" s="10">
-        <f t="shared" si="2"/>
-        <v>4.8615012142857137E-7</v>
+        <f>AVERAGE(I9,I11,I13,I15,I17,I19,I21,I23,I25,I27,I29,I31,I33,I35)</f>
+        <v>4.8175112142857149E-7</v>
       </c>
       <c r="J40" s="11" t="s">
         <v>20</v>
@@ -5457,12 +10599,12 @@
         <v>2.3400000000000002E-9</v>
       </c>
       <c r="H41" s="8">
-        <f t="shared" ref="H41" si="3">MEDIAN(H9,H11,H13,H15,H17,H19,H21,H23,H25,H27,H29,H31,H33,H35)</f>
+        <f>MEDIAN(H9,H11,H13,H15,H17,H19,H21,H23,H25,H27,H29,H31,H33,H35)</f>
         <v>1.625E-12</v>
       </c>
       <c r="I41" s="8">
         <f>MEDIAN(I9,I11,I13,I15,I17,I19,I21,I23,I25,I27,I29,I31,I33,I35)</f>
-        <v>1.4E-8</v>
+        <v>1.3899999999999999E-8</v>
       </c>
       <c r="J41" s="11" t="s">
         <v>21</v>
@@ -5481,6 +10623,19 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="D22:D25"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="D26:D29"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="D30:D33"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E32:E33"/>
     <mergeCell ref="D16:D19"/>
     <mergeCell ref="E16:E17"/>
     <mergeCell ref="E18:E19"/>
@@ -5490,19 +10645,6 @@
     <mergeCell ref="D12:D15"/>
     <mergeCell ref="E12:E13"/>
     <mergeCell ref="E14:E15"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="D26:D29"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="D30:D33"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="D22:D25"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="E24:E25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/optimized_benchmark_results/shaker_benchmark.xlsx
+++ b/optimized_benchmark_results/shaker_benchmark.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\afons\OneDrive - Universidade de Lisboa\Controlo de Plataforma Sismica\minimesa_data\optimized_benchmark_results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B96E7C7-A2C2-4F24-B057-A270A76C9A3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{138CA3BD-7B6B-454C-BFB7-1D02893D9E76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-60" yWindow="-60" windowWidth="28920" windowHeight="16320" activeTab="1" xr2:uid="{40A5E321-79F6-4163-A8DE-342D0D4D7873}"/>
   </bookViews>
@@ -2985,6 +2985,817 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-PT"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.17734249432788887"/>
+          <c:y val="3.529788079476457E-2"/>
+          <c:w val="0.81091179267250157"/>
+          <c:h val="0.6457875809406699"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Folha1!$K$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>OLI 3rd</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="00B0F0"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="00B0F0"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="00B0F0"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Folha1!$J$8:$J$37</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(Folha1!$J$8,Folha1!$J$10,Folha1!$J$12,Folha1!$J$14,Folha1!$J$16,Folha1!$J$18,Folha1!$J$20,Folha1!$J$22,Folha1!$J$24,Folha1!$J$26,Folha1!$J$28,Folha1!$J$30,Folha1!$J$32,Folha1!$J$34,Folha1!$J$36)</c:f>
+              <c:strCache>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>El Centro (FN)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>El Centro (FP)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Erzikan (NS)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Erzikan (EW)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Kobe (NS)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Kobe (EW)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>L'Aquila</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Newhall (FN)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Newhall (FP)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Rinaldi (FN)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Rinaldi (FP)</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Sylmar (FN)</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Sylmar (FP)</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Tolmezzo</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Average</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Folha1!$K$8:$K$37</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(Folha1!$K$8,Folha1!$K$10,Folha1!$K$12,Folha1!$K$14,Folha1!$K$16,Folha1!$K$18,Folha1!$K$20,Folha1!$K$22,Folha1!$K$24,Folha1!$K$26,Folha1!$K$28,Folha1!$K$30,Folha1!$K$32,Folha1!$K$34,Folha1!$K$36)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>-4.3089185078770313</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-5.017728766960432</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-5.4248121550723392</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-5.1487416512809245</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-4.7212463990471711</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-4.7670038896078459</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-4.3957739469155301</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-4.8416375079047507</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-4.6003262785189616</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-4.4089353929735005</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-4.1870866433571443</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-4.3001622741327541</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-5.0083309926200519</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-2.7772835288524167</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-3.840933642603702</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-DC63-4EF5-9EFF-99F2CBA012A4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Folha1!$L$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>PID-F</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Folha1!$J$8:$J$37</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(Folha1!$J$8,Folha1!$J$10,Folha1!$J$12,Folha1!$J$14,Folha1!$J$16,Folha1!$J$18,Folha1!$J$20,Folha1!$J$22,Folha1!$J$24,Folha1!$J$26,Folha1!$J$28,Folha1!$J$30,Folha1!$J$32,Folha1!$J$34,Folha1!$J$36)</c:f>
+              <c:strCache>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>El Centro (FN)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>El Centro (FP)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Erzikan (NS)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Erzikan (EW)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Kobe (NS)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Kobe (EW)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>L'Aquila</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Newhall (FN)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Newhall (FP)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Rinaldi (FN)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Rinaldi (FP)</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Sylmar (FN)</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Sylmar (FP)</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Tolmezzo</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Average</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Folha1!$L$8:$L$37</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(Folha1!$L$8,Folha1!$L$10,Folha1!$L$12,Folha1!$L$14,Folha1!$L$16,Folha1!$L$18,Folha1!$L$20,Folha1!$L$22,Folha1!$L$24,Folha1!$L$26,Folha1!$L$28,Folha1!$L$30,Folha1!$L$32,Folha1!$L$34,Folha1!$L$36)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>-4.2502636844309389</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-4.8794260687941504</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-5.6989700043360187</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-5.3861581781239307</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-4.5086383061657269</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-4.6798537138889458</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-4.7033348097384691</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-4.8728952016351927</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-5.1706962271689747</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-4.7447274948966935</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-4.2298847052128981</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-4.7304870557820839</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-5.3027706572402824</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-3.5171264163912461</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-4.3888535048526878</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-DC63-4EF5-9EFF-99F2CBA012A4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Folha1!$M$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>LQI</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="FFC000"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Folha1!$J$8:$J$37</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(Folha1!$J$8,Folha1!$J$10,Folha1!$J$12,Folha1!$J$14,Folha1!$J$16,Folha1!$J$18,Folha1!$J$20,Folha1!$J$22,Folha1!$J$24,Folha1!$J$26,Folha1!$J$28,Folha1!$J$30,Folha1!$J$32,Folha1!$J$34,Folha1!$J$36)</c:f>
+              <c:strCache>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>El Centro (FN)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>El Centro (FP)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Erzikan (NS)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Erzikan (EW)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Kobe (NS)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Kobe (EW)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>L'Aquila</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Newhall (FN)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Newhall (FP)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Rinaldi (FN)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Rinaldi (FP)</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Sylmar (FN)</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Sylmar (FP)</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Tolmezzo</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Average</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Folha1!$M$8:$M$37</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(Folha1!$M$8,Folha1!$M$10,Folha1!$M$12,Folha1!$M$14,Folha1!$M$16,Folha1!$M$18,Folha1!$M$20,Folha1!$M$22,Folha1!$M$24,Folha1!$M$26,Folha1!$M$28,Folha1!$M$30,Folha1!$M$32,Folha1!$M$34,Folha1!$M$36)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>-4.9546770212133424</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-5.519993057042849</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-6.4168012260313771</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-7.1530446749801762</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-6.5114492834995561</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-5.924453038607469</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-6.3851027839668655</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-6.0515870342213987</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-5.79317412396815</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-5.5718652059712115</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-4.3645162531850881</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-5.5100415205751654</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-6.3665315444204138</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-4.0584885673655968</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-4.9536127119580806</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-DC63-4EF5-9EFF-99F2CBA012A4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1230024880"/>
+        <c:axId val="1230026800"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1230024880"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="high"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-PT"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1230026800"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1230026800"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="-2.5"/>
+          <c:min val="-8"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="pt-PT"/>
+                  <a:t>Acceleration Response Spectrum MSE (m s</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="pt-PT" baseline="30000"/>
+                  <a:t>-2</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="pt-PT"/>
+                  <a:t>)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="1.2355920968811033E-2"/>
+              <c:y val="0.18498971108067039"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-PT"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="[=-3]&quot;10⁻³&quot;;[=-8]&quot;10⁻⁸&quot;" sourceLinked="0"/>
+        <c:majorTickMark val="cross"/>
+        <c:minorTickMark val="out"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-PT"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1230024880"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="5"/>
+        <c:minorUnit val="1"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.50355182575512458"/>
+          <c:y val="0.92081590851569173"/>
+          <c:w val="0.49644831430277098"/>
+          <c:h val="7.4286458754076759E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-PT"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="800">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+          <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="pt-PT"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
@@ -9076,6 +9887,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors12.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -10429,6 +11280,522 @@
 </file>
 
 <file path=xl/charts/style11.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style12.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -15491,6 +16858,44 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>39688</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>145521</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>69006</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>3813</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Gráfico 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F270BDE-1B55-432C-B279-3EC3FD5AC7B4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -16508,6 +17913,20 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="D8:D11"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="D12:D15"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="D30:D33"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="D34:D37"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="E36:E37"/>
     <mergeCell ref="E24:E25"/>
     <mergeCell ref="D26:D29"/>
     <mergeCell ref="E26:E27"/>
@@ -16519,20 +17938,6 @@
     <mergeCell ref="D20:D23"/>
     <mergeCell ref="E20:E21"/>
     <mergeCell ref="E22:E23"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="D30:D33"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="D34:D37"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="D8:D11"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="D12:D15"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="E14:E15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -17835,15 +19240,13 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="A26:A29"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="D8:D11"/>
+    <mergeCell ref="D12:D15"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="D26:D29"/>
+    <mergeCell ref="D30:D33"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="D22:D25"/>
     <mergeCell ref="D36:D37"/>
     <mergeCell ref="D16:D19"/>
     <mergeCell ref="A8:A11"/>
@@ -17860,13 +19263,15 @@
     <mergeCell ref="A22:A25"/>
     <mergeCell ref="B22:B23"/>
     <mergeCell ref="B24:B25"/>
-    <mergeCell ref="D8:D11"/>
-    <mergeCell ref="D12:D15"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="D26:D29"/>
-    <mergeCell ref="D30:D33"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="D22:D25"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="B34:B35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
